--- a/data/trans_bre/IP12-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 6,49</t>
+          <t>-4,06; 6,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 11,86</t>
+          <t>-0,12; 11,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 6,61</t>
+          <t>-3,23; 6,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 6,7</t>
+          <t>-3,54; 7,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 130,91</t>
+          <t>-41,22; 124,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 259,11</t>
+          <t>-6,65; 239,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,16; 258,0</t>
+          <t>-49,07; 268,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-48,74; 148,57</t>
+          <t>-43,36; 208,3</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 1,93</t>
+          <t>-5,51; 2,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 7,63</t>
+          <t>-1,29; 7,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 6,99</t>
+          <t>-1,36; 7,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 4,51</t>
+          <t>-3,63; 4,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,84; 31,34</t>
+          <t>-54,62; 45,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 160,86</t>
+          <t>-16,74; 174,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 142,83</t>
+          <t>-15,49; 135,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 85,82</t>
+          <t>-45,29; 87,6</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 8,78</t>
+          <t>-0,8; 8,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 0,1</t>
+          <t>-9,78; 0,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 3,19</t>
+          <t>-6,69; 3,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 4,32</t>
+          <t>-7,21; 4,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 243,52</t>
+          <t>-22,27; 247,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,81; 5,33</t>
+          <t>-70,0; 11,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,19; 48,97</t>
+          <t>-55,6; 45,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,77; 73,4</t>
+          <t>-61,25; 75,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 1,3</t>
+          <t>-4,94; 1,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 2,12</t>
+          <t>-7,6; 1,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,87</t>
+          <t>-1,43; 6,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 1,46</t>
+          <t>-8,41; 0,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,72; 47,82</t>
+          <t>-73,67; 64,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,21; 28,47</t>
+          <t>-58,19; 26,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 202,72</t>
+          <t>-25,26; 226,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,13; 30,83</t>
+          <t>-68,57; 12,34</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,92</t>
+          <t>-2,15; 2,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,66</t>
+          <t>-2,3; 2,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,59</t>
+          <t>-0,92; 3,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,02</t>
+          <t>-3,41; 1,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 34,59</t>
+          <t>-29,14; 37,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 38,39</t>
+          <t>-24,42; 35,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 66,05</t>
+          <t>-13,28; 69,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,8; 31,32</t>
+          <t>-37,01; 24,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 6,38</t>
+          <t>-4,1; 7,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 11,4</t>
+          <t>0,47; 11,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 6,68</t>
+          <t>-3,42; 6,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 7,47</t>
+          <t>-3,8; 6,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 124,81</t>
+          <t>-42,35; 128,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 239,18</t>
+          <t>1,63; 280,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-49,07; 268,82</t>
+          <t>-52,28; 228,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 208,3</t>
+          <t>-45,73; 169,41</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 2,37</t>
+          <t>-5,65; 2,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 7,37</t>
+          <t>-1,34; 7,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 7,06</t>
+          <t>-1,39; 6,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,44</t>
+          <t>-3,33; 4,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 45,71</t>
+          <t>-56,17; 44,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 174,89</t>
+          <t>-17,79; 173,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 135,59</t>
+          <t>-17,68; 131,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,29; 87,6</t>
+          <t>-41,97; 97,15</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 8,6</t>
+          <t>-0,6; 8,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 0,69</t>
+          <t>-9,78; 0,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 3,12</t>
+          <t>-6,74; 3,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 4,21</t>
+          <t>-7,34; 4,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 247,11</t>
+          <t>-11,71; 249,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,0; 11,2</t>
+          <t>-71,34; 6,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,6; 45,25</t>
+          <t>-53,89; 46,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,25; 75,37</t>
+          <t>-58,04; 77,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 1,76</t>
+          <t>-5,04; 1,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 1,83</t>
+          <t>-7,47; 1,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 6,37</t>
+          <t>-1,2; 6,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 0,63</t>
+          <t>-8,35; 1,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,67; 64,81</t>
+          <t>-75,62; 46,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,19; 26,41</t>
+          <t>-58,14; 26,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 226,03</t>
+          <t>-22,64; 221,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,57; 12,34</t>
+          <t>-66,1; 26,12</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,2</t>
+          <t>-2,13; 2,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,58</t>
+          <t>-2,32; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,61</t>
+          <t>-0,75; 3,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,66</t>
+          <t>-3,1; 1,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 37,08</t>
+          <t>-28,68; 39,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 35,66</t>
+          <t>-24,44; 34,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 69,14</t>
+          <t>-9,82; 68,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 24,54</t>
+          <t>-35,27; 23,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 7,0</t>
+          <t>-3,81; 6,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 11,77</t>
+          <t>0,01; 11,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 6,75</t>
+          <t>-3,15; 6,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 6,56</t>
+          <t>-4,86; 6,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,35; 128,57</t>
+          <t>-39,99; 130,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 280,58</t>
+          <t>-4,47; 259,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-52,28; 228,93</t>
+          <t>-48,16; 258,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 169,41</t>
+          <t>-51,14; 142,0</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 2,18</t>
+          <t>-5,85; 1,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,74</t>
+          <t>-0,83; 7,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 6,97</t>
+          <t>-1,28; 6,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 4,49</t>
+          <t>-3,95; 4,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,17; 44,18</t>
+          <t>-58,84; 31,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 173,24</t>
+          <t>-15,86; 160,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 131,59</t>
+          <t>-14,45; 142,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,97; 97,15</t>
+          <t>-45,65; 74,92</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-11,77%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 8,56</t>
+          <t>-1,0; 8,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 0,34</t>
+          <t>-9,82; 0,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 3,21</t>
+          <t>-6,82; 3,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 4,41</t>
+          <t>-6,06; 6,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 249,69</t>
+          <t>-17,97; 243,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,34; 6,86</t>
+          <t>-70,81; 5,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-53,89; 46,14</t>
+          <t>-54,19; 48,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,04; 77,37</t>
+          <t>-48,83; 103,85</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>-2,91</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-34,34%</t>
+          <t>-32,36%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,39</t>
+          <t>-5,13; 1,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 1,86</t>
+          <t>-7,33; 2,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 6,66</t>
+          <t>-1,18; 5,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 1,36</t>
+          <t>-8,24; 1,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,62; 46,3</t>
+          <t>-74,72; 47,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,14; 26,83</t>
+          <t>-58,21; 28,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 221,05</t>
+          <t>-21,21; 202,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,1; 26,12</t>
+          <t>-65,67; 35,36</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-8,4%</t>
+          <t>-6,16%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,07</t>
+          <t>-2,21; 1,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,55</t>
+          <t>-2,15; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,63</t>
+          <t>-0,75; 3,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,47</t>
+          <t>-3,06; 2,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 39,18</t>
+          <t>-29,64; 34,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 34,03</t>
+          <t>-22,12; 38,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 68,11</t>
+          <t>-10,04; 66,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 23,05</t>
+          <t>-33,67; 32,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,7</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>86,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13,06%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.123724630517908</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5.69953443589752</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.828337452914291</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.8679102887200696</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1459336091269608</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.8633681639465687</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.3803287690026634</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1306037317674107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,81; 6,49</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,01; 11,86</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,15; 6,61</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,86; 6,28</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-39,99; 130,91</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-4,47; 259,11</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-48,16; 258,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-51,14; 142,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.806098745883545</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.01111772976361799</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.151087676157872</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.860634411798491</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3998563915841091</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.04467539065969665</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.481584575016587</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.5113898421679915</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.490786723287292</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>11.86133012614095</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.611377263315014</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.281460314757764</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.309136046863366</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.591135743378375</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2.580034921166644</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.419970987911299</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,74</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,98</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-21,9%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>47,3%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>36,05%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,85; 1,93</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,83; 7,63</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,28; 6,99</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,95; 4,15</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-58,84; 31,34</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-15,86; 160,86</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-14,45; 142,83</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-45,65; 74,92</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.737269020284993</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.98499172365455</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.599851620953279</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.02613735932539551</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2189544276344204</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.4729949677498956</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.3604938983631477</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.003802299141977771</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,68</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,75</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-44,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-18,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.852160793111178</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.8343765622998154</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.27828606633373</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.948845860671969</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5884496305972049</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.158592359897461</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1444611752501622</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4565377808068131</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,0; 8,78</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-9,82; 0,1</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,82; 3,19</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,06; 6,05</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-17,97; 243,52</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-70,81; 5,33</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-54,19; 48,97</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-48,83; 103,85</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.927206624017777</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.632849417217775</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.993257318394395</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.146470973126459</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3134135393864236</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.608582236504794</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.428310200875473</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.7492307476541729</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,78</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,73</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,44</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,91</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-35,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-26,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-32,36%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.681989920835371</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-4.815183664218402</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.748925101584541</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.1810582119121523</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.665673704685907</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.4427633298519924</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.1828414408343013</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.01968623880878912</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,13; 1,3</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-7,33; 2,12</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,18; 5,87</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,24; 1,72</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-74,72; 47,82</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-58,21; 28,47</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-21,21; 202,72</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-65,67; 35,36</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.000504995462847</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-9.819227652236115</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.822143085445669</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.0558606699734</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1796732862115353</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.7080920411828606</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.5419030140199065</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4883247664765734</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.776882204444956</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.09564179317110279</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.188186213359231</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.048979544886294</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.435170728730103</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.05330997100431782</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.4897181355972739</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.038518441828228</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.779973737033016</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.733215277900623</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.444533851496818</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.913438073181569</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3524729232862422</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2698745081087406</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.5442792128237455</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.323612345085518</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.134005387892538</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-7.331631242177729</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.177973521301778</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.235429617493493</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7471684354245424</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5821229963988364</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2121086340209999</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6566978783787624</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.297248356942261</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.118763646926681</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.873908489741532</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.721536497315717</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4782187475214259</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2847077089925225</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.027221994969187</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3536436581328488</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,75%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-6,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,21; 1,92</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,15; 2,66</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,75; 3,59</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,06; 2,06</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-29,64; 34,59</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-22,12; 38,39</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-10,04; 66,05</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-33,67; 32,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.1147717697033451</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1804613539378427</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.40937149207503</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.487199138722888</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.01750188384014395</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.02139362066414612</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.2165263762158409</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.06162787995729137</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.206801419605962</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.151125009023063</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.7479569944202287</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.061571389417888</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2964060674268426</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2212374071580492</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1003701485290753</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3366875108256424</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.917584850197737</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.662645364972534</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.592376150912641</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.056827975774822</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.345938939269315</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3838738921770491</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.6605083465516295</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3226190118822938</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
